--- a/artfynd/A 3483-2026 artfynd.xlsx
+++ b/artfynd/A 3483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>100977008</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720529.3836996935</v>
+        <v>720530</v>
       </c>
       <c r="R2" t="n">
-        <v>7074719.844119479</v>
+        <v>7074720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100977006</v>
+        <v>100977007</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720492.0514209591</v>
+        <v>720542</v>
       </c>
       <c r="R3" t="n">
-        <v>7074687.454878501</v>
+        <v>7074724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +859,9 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100977007</v>
+        <v>100977006</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720542.4504087105</v>
+        <v>720492</v>
       </c>
       <c r="R4" t="n">
-        <v>7074723.870464705</v>
+        <v>7074687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +975,9 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,137 +1016,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>100977005</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>720543.3359839348</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7074723.932527783</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 3483-2026 artfynd.xlsx
+++ b/artfynd/A 3483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100977008</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100977007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100977006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>